--- a/tests/fixtures/m0/hdfc_holdings_sample.xlsx
+++ b/tests/fixtures/m0/hdfc_holdings_sample.xlsx
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>11073641.17999999</v>
+        <v>2742524.92</v>
       </c>
       <c r="H24" t="n">
         <v>99.99999999999996</v>
